--- a/hardware/lumigate_CPL.xlsx
+++ b/hardware/lumigate_CPL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.2389mm</t>
+          <t>15.1690mm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.5750mm</t>
+          <t>9.0828mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14.0750mm</t>
+          <t>12.5750mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12.5750mm</t>
+          <t>11.0750mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -526,12 +526,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42.2389mm</t>
+          <t>43.2389mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16.5750mm</t>
+          <t>16.0750mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -551,12 +551,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>45.2389mm</t>
+          <t>45.7389mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16.5750mm</t>
+          <t>18.5750mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.2389mm</t>
+          <t>50.7389mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22.5750mm</t>
+          <t>24.0750mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11.0750mm</t>
+          <t>9.0750mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.0750mm</t>
+          <t>3.5750mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.0750mm</t>
+          <t>3.5750mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>47.7189mm</t>
+          <t>48.7189mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.0750mm</t>
+          <t>3.5750mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>51.2189mm</t>
+          <t>52.2189mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>31.2189mm</t>
+          <t>28.7189mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7.1000mm</t>
+          <t>6.6000mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>39.7389mm</t>
+          <t>42.2389mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10.5750mm</t>
+          <t>11.0750mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17.0750mm</t>
+          <t>16.5750mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15.5750mm</t>
+          <t>14.5750mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>51.2189mm</t>
+          <t>51.7689mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>37.6375mm</t>
+          <t>38.0125mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>39.8889mm</t>
+          <t>37.5489mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1196,17 +1196,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>23.1189mm</t>
+          <t>29.2189mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16.0750mm</t>
+          <t>30.5750mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1215,23 +1215,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PS1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>39.1989mm</t>
+          <t>24.1189mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>43.9950mm</t>
+          <t>22.0750mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1246,17 +1246,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>PS1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9.6564mm</t>
+          <t>41.6989mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13.6250mm</t>
+          <t>44.4950mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1265,13 +1265,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>17.6250mm</t>
+          <t>13.6250mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1296,17 +1296,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13.2089mm</t>
+          <t>9.6564mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>16.5750mm</t>
+          <t>17.6250mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1315,23 +1315,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>38.2089mm</t>
+          <t>15.1590mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>23.5750mm</t>
+          <t>15.0828mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1346,12 +1346,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>31.7089mm</t>
+          <t>38.2089mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1365,23 +1365,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>51.6314mm</t>
+          <t>31.7089mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>33.0750mm</t>
+          <t>23.5750mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1396,17 +1396,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.7189mm</t>
+          <t>51.6314mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>45.5850mm</t>
+          <t>33.0750mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1415,18 +1415,18 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5.2189mm</t>
+          <t>2.7189mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1446,12 +1446,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7.7189mm</t>
+          <t>5.2189mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1471,17 +1471,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10.2189mm</t>
+          <t>7.7189mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>45.5850mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1496,17 +1496,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12.7189mm</t>
+          <t>10.2189mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>45.5850mm</t>
+          <t>45.5750mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1521,17 +1521,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>45.2289mm</t>
+          <t>12.7189mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9.0750mm</t>
+          <t>45.5850mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1540,23 +1540,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13.2089mm</t>
+          <t>47.2089mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>15.0750mm</t>
+          <t>5.0750mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1565,23 +1565,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>27.7189mm</t>
+          <t>15.1390mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>19.0650mm</t>
+          <t>13.0828mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1590,23 +1590,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>45.2089mm</t>
+          <t>27.7189mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12.0750mm</t>
+          <t>17.5850mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1615,23 +1615,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>45.2289mm</t>
+          <t>45.7089mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10.5750mm</t>
+          <t>11.0750mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1646,17 +1646,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13.2089mm</t>
+          <t>46.2089mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>19.0750mm</t>
+          <t>8.0750mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1671,17 +1671,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13.2089mm</t>
+          <t>15.1390mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>17.5750mm</t>
+          <t>20.5828mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1696,17 +1696,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13.2089mm</t>
+          <t>15.1390mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12.0750mm</t>
+          <t>17.0828mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1721,17 +1721,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13.2089mm</t>
+          <t>28.7089mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>13.5750mm</t>
+          <t>2.5750mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1746,17 +1746,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24.2189mm</t>
+          <t>42.7089mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>47.5750mm</t>
+          <t>9.0750mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1765,23 +1765,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>SW1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>28.7189mm</t>
+          <t>16.7189mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>47.5750mm</t>
+          <t>48.0750mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1796,17 +1796,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>SW2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10.0989mm</t>
+          <t>20.7189mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>32.3250mm</t>
+          <t>48.0750mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1815,23 +1815,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>35.4689mm</t>
+          <t>10.0989mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>15.8250mm</t>
+          <t>32.3250mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1840,23 +1840,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23.8489mm</t>
+          <t>35.4689mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>7.1250mm</t>
+          <t>15.8250mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1871,17 +1871,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17.9189mm</t>
+          <t>22.3489mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>18.1250mm</t>
+          <t>7.6250mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1890,23 +1890,23 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>38.9689mm</t>
+          <t>21.4189mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>36.1250mm</t>
+          <t>16.1250mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1915,31 +1915,56 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>42.4689mm</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>36.1250mm</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>43.8439mm</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>19.8750mm</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>44.3439mm</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>22.8750mm</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
         <v>0</v>
       </c>
     </row>

--- a/hardware/lumigate_CPL.xlsx
+++ b/hardware/lumigate_CPL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.1690mm</t>
+          <t>2.4709mm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.0828mm</t>
+          <t>20.6511mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -464,8 +464,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -476,12 +478,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.7389mm</t>
+          <t>26.2532mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12.5750mm</t>
+          <t>-0.4711mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -489,8 +491,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -501,12 +505,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.7389mm</t>
+          <t>24.6337mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11.0750mm</t>
+          <t>-6.5993mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -514,8 +518,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -526,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.2389mm</t>
+          <t>36.6917mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16.0750mm</t>
+          <t>-16.9242mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -539,8 +545,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>180</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -551,12 +559,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>45.7389mm</t>
+          <t>27.3515mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18.5750mm</t>
+          <t>-17.7241mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -564,8 +572,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -576,12 +586,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.7389mm</t>
+          <t>20.1139mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>24.0750mm</t>
+          <t>-7.9919mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,8 +599,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -601,12 +613,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.7389mm</t>
+          <t>25.6602mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.0750mm</t>
+          <t>34.9368mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -614,8 +626,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -626,12 +640,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8.7689mm</t>
+          <t>56.1811mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.5750mm</t>
+          <t>-14.1064mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -639,8 +653,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -651,12 +667,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.7689mm</t>
+          <t>66.2189mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.5750mm</t>
+          <t>-12.6250mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -664,8 +680,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -676,12 +694,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8.7389mm</t>
+          <t>52.9722mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11.0750mm</t>
+          <t>31.0683mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -689,8 +707,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -701,12 +721,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>48.7189mm</t>
+          <t>70.3856mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>43.0950mm</t>
+          <t>31.0683mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -714,8 +734,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>90</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -726,12 +748,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12.7689mm</t>
+          <t>7.0650mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.5750mm</t>
+          <t>19.5266mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -739,8 +761,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -751,12 +775,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>52.2189mm</t>
+          <t>71.0995mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>42.6000mm</t>
+          <t>36.0306mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -764,8 +788,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>90</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -776,12 +802,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28.7189mm</t>
+          <t>51.3189mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.6000mm</t>
+          <t>38.8750mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -789,8 +815,10 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>90</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -801,12 +829,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>45.1989mm</t>
+          <t>21.1996mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13.5750mm</t>
+          <t>-0.4461mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -814,24 +842,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.7389mm</t>
+          <t>53.1197mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.5750mm</t>
+          <t>0.1583mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -839,24 +869,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>42.2389mm</t>
+          <t>70.5331mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11.0750mm</t>
+          <t>0.1583mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -864,24 +896,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27.7389mm</t>
+          <t>71.5389mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14.5750mm</t>
+          <t>5.3941mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -889,24 +923,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>34.7389mm</t>
+          <t>47.3189mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23.5750mm</t>
+          <t>34.0750mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -914,24 +950,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.7389mm</t>
+          <t>44.2189mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16.5750mm</t>
+          <t>-1.4250mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -939,24 +977,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.7189mm</t>
+          <t>13.6720mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14.5750mm</t>
+          <t>6.2447mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -964,24 +1004,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>51.7689mm</t>
+          <t>13.7189mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>38.0125mm</t>
+          <t>12.1250mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -989,24 +1031,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>270</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.6810mm</t>
+          <t>2.2491mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>48.5550mm</t>
+          <t>17.7135mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1014,24 +1058,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>270</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5.1905mm</t>
+          <t>7.4177mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>48.5625mm</t>
+          <t>3.9670mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1039,24 +1085,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>270</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7.7000mm</t>
+          <t>10.0189mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>48.5700mm</t>
+          <t>6.5750mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1064,24 +1112,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>270</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10.2094mm</t>
+          <t>24.6337mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>48.5775mm</t>
+          <t>-10.7507mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1089,24 +1139,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>270</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12.7189mm</t>
+          <t>24.2104mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>48.5850mm</t>
+          <t>-13.7374mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1114,24 +1166,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>270</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>59.7889mm</t>
+          <t>24.6909mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>36.9250mm</t>
+          <t>-3.6118mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1139,24 +1193,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>90</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>37.5489mm</t>
+          <t>34.6218mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4.0450mm</t>
+          <t>-1.3550mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1164,24 +1220,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>62.1789mm</t>
+          <t>30.0735mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11.7750mm</t>
+          <t>-1.2230mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1189,24 +1247,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>270</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>J4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29.2189mm</t>
+          <t>74.6564mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>30.5750mm</t>
+          <t>32.0250mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1214,24 +1274,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>180</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>24.1189mm</t>
+          <t>27.2189mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22.0750mm</t>
+          <t>25.0750mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1239,24 +1301,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PS1</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>41.6989mm</t>
+          <t>51.2189mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>44.4950mm</t>
+          <t>-9.9250mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1264,24 +1328,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9.6564mm</t>
+          <t>24.1810mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>13.6250mm</t>
+          <t>48.5450mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1289,24 +1355,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>180</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9.6564mm</t>
+          <t>26.6905mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17.6250mm</t>
+          <t>48.5525mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1314,24 +1382,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>180</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15.1590mm</t>
+          <t>29.2000mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15.0828mm</t>
+          <t>48.5600mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1339,24 +1409,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>38.2089mm</t>
+          <t>31.7094mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>23.5750mm</t>
+          <t>48.5675mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1364,24 +1436,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>31.7089mm</t>
+          <t>34.2189mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>23.5750mm</t>
+          <t>48.5750mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1389,24 +1463,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>180</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>51.6314mm</t>
+          <t>75.2814mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>33.0750mm</t>
+          <t>1.0750mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1414,24 +1490,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>180</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.7189mm</t>
+          <t>37.2189mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>45.5850mm</t>
+          <t>-23.3250mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1439,24 +1517,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>90</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5.2189mm</t>
+          <t>51.6389mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>45.5850mm</t>
+          <t>35.5750mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1464,24 +1544,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>90</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>FB2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7.7189mm</t>
+          <t>71.5932mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>45.5850mm</t>
+          <t>39.7476mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1489,24 +1571,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>90</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>FB3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10.2189mm</t>
+          <t>71.9558mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>45.5750mm</t>
+          <t>9.1748mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1514,24 +1598,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>90</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R17</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12.7189mm</t>
+          <t>88.7189mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>45.5850mm</t>
+          <t>29.0750mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1539,24 +1625,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>90</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>47.2089mm</t>
+          <t>44.7189mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5.0750mm</t>
+          <t>-22.2350mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1564,24 +1652,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15.1390mm</t>
+          <t>8.9589mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>13.0828mm</t>
+          <t>-6.4250mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1589,24 +1679,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>180</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>J4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>27.7189mm</t>
+          <t>47.2189mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>17.5850mm</t>
+          <t>8.0750mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1614,24 +1706,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>90</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>45.7089mm</t>
+          <t>88.8764mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>11.0750mm</t>
+          <t>-1.9250mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1639,24 +1733,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>J6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>46.2089mm</t>
+          <t>47.2189mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8.0750mm</t>
+          <t>21.5750mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1664,24 +1760,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>0</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>J7</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15.1390mm</t>
+          <t>73.4189mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>20.5828mm</t>
+          <t>25.4500mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1689,24 +1787,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>J8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15.1390mm</t>
+          <t>72.9189mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>17.0828mm</t>
+          <t>-6.0500mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1714,24 +1814,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E52" t="n">
-        <v>0</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>28.7089mm</t>
+          <t>66.2189mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2.5750mm</t>
+          <t>-16.5250mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1739,24 +1841,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E53" t="n">
-        <v>0</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>42.7089mm</t>
+          <t>76.2689mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>9.0750mm</t>
+          <t>39.6750mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1764,24 +1868,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SW1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16.7189mm</t>
+          <t>76.7189mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>48.0750mm</t>
+          <t>9.0750mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1789,24 +1895,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E55" t="n">
-        <v>270</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SW2</t>
+          <t>PS1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20.7189mm</t>
+          <t>60.9089mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>48.0750mm</t>
+          <t>35.5750mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1814,24 +1922,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>270</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>PS2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10.0989mm</t>
+          <t>61.2664mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>32.3250mm</t>
+          <t>5.2450mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1839,24 +1949,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E57" t="n">
-        <v>90</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>35.4689mm</t>
+          <t>42.6689mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>15.8250mm</t>
+          <t>37.5125mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1864,24 +1976,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E58" t="n">
-        <v>270</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22.3489mm</t>
+          <t>42.6689mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>7.6250mm</t>
+          <t>32.0125mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1889,24 +2003,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E59" t="n">
-        <v>270</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21.4189mm</t>
+          <t>6.5025mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>16.1250mm</t>
+          <t>16.1790mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1914,24 +2030,26 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E60" t="n">
-        <v>0</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>42.4689mm</t>
+          <t>62.7189mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>36.1250mm</t>
+          <t>-19.4350mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1939,33 +2057,793 @@
           <t>Top</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>270</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>59.5972mm</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-19.4350mm</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>76.3064mm</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>36.0750mm</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>24.2189mm</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>45.5750mm</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>26.7189mm</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>45.5750mm</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>29.2189mm</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>45.5750mm</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>31.7189mm</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>45.5650mm</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>34.2189mm</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>45.5750mm</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>20.4231mm</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>-3.3763mm</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>76.8064mm</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>5.5750mm</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>18.1501mm</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>44.5248mm</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>30.1398mm</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1.9487mm</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>9.7089mm</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>-16.4250mm</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3.0686mm</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4.9674mm</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>37.7885mm</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>36.4263mm</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>37.9994mm</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>32.4249mm</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>42.2289mm</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>-16.1350mm</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>47.0389mm</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>-14.1050mm</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SW1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>11.2189mm</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>46.8750mm</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SW2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>15.2189mm</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>46.8750mm</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10.4889mm</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>32.5750mm</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>32.4689mm</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>-8.6750mm</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>31.7189mm</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>34.5750mm</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>60.8021mm</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>-15.9759mm</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>61.6789mm</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>27.2050mm</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>61.8264mm</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>-3.7050mm</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>U7</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>27.2189mm</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>12.5750mm</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>U8</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>41.7192mm</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>-12.2524mm</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>6.7189mm</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>6.5750mm</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>44.3439mm</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>22.8750mm</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>31.9605mm</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>-17.3174mm</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
